--- a/data/trans_dic/P16-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,0; 64,02</t>
+          <t>57,88; 64,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,66; 74,65</t>
+          <t>68,9; 74,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,9; 71,66</t>
+          <t>64,73; 71,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66,16; 74,29</t>
+          <t>66,42; 74,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,19; 78,64</t>
+          <t>74,13; 78,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,96; 86,96</t>
+          <t>82,85; 87,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,16; 86,75</t>
+          <t>82,18; 86,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80,8; 85,36</t>
+          <t>80,93; 85,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,68; 71,56</t>
+          <t>67,76; 71,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77,76; 81,24</t>
+          <t>77,66; 81,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75,44; 79,4</t>
+          <t>75,39; 79,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,86; 79,95</t>
+          <t>75,85; 79,96</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,26; 32,58</t>
+          <t>28,21; 32,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,84; 44,45</t>
+          <t>39,97; 44,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,01; 46,3</t>
+          <t>42,06; 46,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,43; 49,65</t>
+          <t>29,2; 49,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,74; 48,71</t>
+          <t>43,69; 48,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,31; 64,24</t>
+          <t>59,57; 64,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,36; 59,91</t>
+          <t>55,41; 59,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,11; 74,02</t>
+          <t>58,03; 73,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,59</t>
+          <t>36,4; 39,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,73; 53,33</t>
+          <t>49,72; 53,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49,1; 52,31</t>
+          <t>49,24; 52,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,08; 58,86</t>
+          <t>44,11; 59,06</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,4; 37,83</t>
+          <t>29,14; 37,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,11; 45,5</t>
+          <t>35,93; 45,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,6; 49,55</t>
+          <t>40,59; 49,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,7; 57,08</t>
+          <t>48,49; 56,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,07; 55,42</t>
+          <t>45,93; 55,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,35; 64,12</t>
+          <t>53,47; 63,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,93; 59,43</t>
+          <t>50,74; 59,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,05; 61,1</t>
+          <t>54,41; 61,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,46; 44,67</t>
+          <t>38,41; 44,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,22; 53,34</t>
+          <t>45,92; 53,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46,57; 53,03</t>
+          <t>46,81; 52,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52,68; 58,04</t>
+          <t>51,91; 57,75</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,87; 42,28</t>
+          <t>39,03; 42,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,65; 52,1</t>
+          <t>48,69; 52,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,86; 51,44</t>
+          <t>47,78; 51,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,86; 53,89</t>
+          <t>38,01; 53,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,74; 60,35</t>
+          <t>56,87; 60,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,64; 71,66</t>
+          <t>68,52; 71,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,25; 66,43</t>
+          <t>63,19; 66,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,38; 72,77</t>
+          <t>63,26; 71,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,45; 50,88</t>
+          <t>48,47; 50,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,15; 61,66</t>
+          <t>59,28; 61,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,15; 58,73</t>
+          <t>56,28; 58,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,41; 61,63</t>
+          <t>51,41; 61,45</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>598408; 660548</t>
+          <t>597178; 662995</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>669162; 727562</t>
+          <t>671507; 729654</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>489578; 540583</t>
+          <t>488256; 540180</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>340708; 382539</t>
+          <t>342020; 384318</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>975644; 1034228</t>
+          <t>974874; 1033469</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1108998; 1162473</t>
+          <t>1107467; 1163494</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>817229; 862855</t>
+          <t>817366; 862630</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>608138; 642465</t>
+          <t>609136; 641583</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1588408; 1679379</t>
+          <t>1590292; 1678361</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1797326; 1877711</t>
+          <t>1795143; 1876562</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1319492; 1388677</t>
+          <t>1318528; 1390542</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>961606; 1013442</t>
+          <t>961502; 1013485</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>478318; 551333</t>
+          <t>477504; 555246</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>780841; 871150</t>
+          <t>783376; 874365</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>872240; 961316</t>
+          <t>873312; 962683</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>696948; 1137088</t>
+          <t>668716; 1137655</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>694465; 773338</t>
+          <t>693674; 768611</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1041960; 1128714</t>
+          <t>1046632; 1129406</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1100770; 1191156</t>
+          <t>1101753; 1192191</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1300053; 1655956</t>
+          <t>1298320; 1634651</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1188890; 1298650</t>
+          <t>1194029; 1301060</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1848353; 1982196</t>
+          <t>1848054; 1974775</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1995699; 2126387</t>
+          <t>2001357; 2128457</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2040823; 2664768</t>
+          <t>1997233; 2673855</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>162139; 208621</t>
+          <t>160663; 208657</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>173448; 218571</t>
+          <t>172597; 220344</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>222028; 271009</t>
+          <t>221990; 271282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314926; 369097</t>
+          <t>313567; 368055</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>219501; 264011</t>
+          <t>218835; 264951</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>244143; 293457</t>
+          <t>244726; 290156</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>279659; 326371</t>
+          <t>278616; 324989</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>356948; 403544</t>
+          <t>359328; 405288</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>395253; 459125</t>
+          <t>394751; 459950</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>433495; 500288</t>
+          <t>430680; 497132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>510426; 581194</t>
+          <t>513069; 578269</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>688570; 758696</t>
+          <t>678460; 754838</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1273254; 1384974</t>
+          <t>1278406; 1386547</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1661440; 1779309</t>
+          <t>1662857; 1786307</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1616497; 1737528</t>
+          <t>1613679; 1736973</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1341312; 1860309</t>
+          <t>1311948; 1851087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1917351; 2039467</t>
+          <t>1921725; 2034112</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2437612; 2544992</t>
+          <t>2433442; 2543822</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2234206; 2346384</t>
+          <t>2231949; 2348766</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2313415; 2656452</t>
+          <t>2308977; 2617178</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3224177; 3385897</t>
+          <t>3225281; 3389671</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4120844; 4295376</t>
+          <t>4129939; 4295748</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3879500; 4057962</t>
+          <t>3889010; 4051138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3651006; 4377187</t>
+          <t>3651235; 4364087</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>57,88; 64,26</t>
+          <t>57,82; 63,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,9; 74,86</t>
+          <t>69,05; 74,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,73; 71,61</t>
+          <t>64,88; 71,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66,42; 74,63</t>
+          <t>63,7; 71,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,13; 78,58</t>
+          <t>73,93; 78,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,85; 87,04</t>
+          <t>83,06; 87,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,18; 86,73</t>
+          <t>82,27; 86,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80,93; 85,25</t>
+          <t>80,0; 84,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,76; 71,52</t>
+          <t>67,75; 71,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77,66; 81,19</t>
+          <t>77,52; 81,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75,39; 79,5</t>
+          <t>75,56; 79,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,85; 79,96</t>
+          <t>74,01; 78,27</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,21; 32,81</t>
+          <t>28,26; 32,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,97; 44,61</t>
+          <t>39,84; 44,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,06; 46,36</t>
+          <t>41,78; 46,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,2; 49,67</t>
+          <t>45,61; 50,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,69; 48,41</t>
+          <t>43,83; 48,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,57; 64,28</t>
+          <t>59,75; 64,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,41; 59,96</t>
+          <t>55,34; 59,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,03; 73,07</t>
+          <t>55,83; 60,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,4; 39,67</t>
+          <t>36,26; 39,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,72; 53,13</t>
+          <t>49,78; 53,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49,24; 52,36</t>
+          <t>49,22; 52,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,11; 59,06</t>
+          <t>51,22; 54,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,14; 37,84</t>
+          <t>29,13; 37,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,93; 45,87</t>
+          <t>35,96; 45,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,59; 49,6</t>
+          <t>40,43; 49,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,49; 56,92</t>
+          <t>48,46; 56,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,93; 55,61</t>
+          <t>46,13; 55,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,47; 63,4</t>
+          <t>53,83; 63,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,74; 59,18</t>
+          <t>50,88; 59,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,41; 61,36</t>
+          <t>54,84; 61,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,41; 44,75</t>
+          <t>38,76; 45,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,92; 53,0</t>
+          <t>45,87; 53,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46,81; 52,76</t>
+          <t>46,94; 53,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,91; 57,75</t>
+          <t>53,0; 58,07</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,97%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,03; 42,33</t>
+          <t>38,75; 42,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,69; 52,31</t>
+          <t>48,72; 52,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,78; 51,43</t>
+          <t>48,05; 51,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,01; 53,63</t>
+          <t>50,53; 54,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,87; 60,2</t>
+          <t>56,82; 60,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,52; 71,63</t>
+          <t>68,51; 71,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,19; 66,5</t>
+          <t>63,13; 66,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,26; 71,7</t>
+          <t>61,84; 64,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,47; 50,94</t>
+          <t>48,5; 50,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,28; 61,66</t>
+          <t>59,29; 61,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,28; 58,63</t>
+          <t>56,22; 58,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,41; 61,45</t>
+          <t>56,81; 59,12</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362797</t>
+          <t>392347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>625858</t>
+          <t>674947</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>988655</t>
+          <t>1067294</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>597178; 662995</t>
+          <t>596534; 660127</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>671507; 729654</t>
+          <t>673026; 725793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>488256; 540180</t>
+          <t>489442; 539450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>342020; 384318</t>
+          <t>368546; 415582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>974874; 1033469</t>
+          <t>972216; 1034261</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1107467; 1163494</t>
+          <t>1110273; 1165593</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>817366; 862630</t>
+          <t>818290; 865147</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>609136; 641583</t>
+          <t>656571; 693833</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1590292; 1678361</t>
+          <t>1590049; 1679282</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1795143; 1876562</t>
+          <t>1791781; 1876418</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1318528; 1390542</t>
+          <t>1321476; 1392167</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>961502; 1013485</t>
+          <t>1035539; 1095177</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>998908</t>
+          <t>1073055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1411180</t>
+          <t>1258329</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2410087</t>
+          <t>2331385</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>477504; 555246</t>
+          <t>478330; 555032</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>783376; 874365</t>
+          <t>780886; 877847</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>873312; 962683</t>
+          <t>867535; 962003</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>668716; 1137655</t>
+          <t>1017316; 1126004</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>693674; 768611</t>
+          <t>695950; 775231</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1046632; 1129406</t>
+          <t>1049695; 1133541</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1101753; 1192191</t>
+          <t>1100268; 1191444</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1298320; 1634651</t>
+          <t>1211959; 1303075</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1194029; 1301060</t>
+          <t>1189415; 1303139</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1848054; 1974775</t>
+          <t>1850167; 1973223</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2001357; 2128457</t>
+          <t>2000689; 2128441</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1997233; 2673855</t>
+          <t>2254193; 2400106</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>340665</t>
+          <t>375679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>381569</t>
+          <t>426671</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>722234</t>
+          <t>802350</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>160663; 208657</t>
+          <t>160606; 207225</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>172597; 220344</t>
+          <t>172706; 220326</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>221990; 271282</t>
+          <t>221119; 270870</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>313567; 368055</t>
+          <t>344858; 403857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>218835; 264951</t>
+          <t>219765; 264612</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>244726; 290156</t>
+          <t>246335; 291945</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>278616; 324989</t>
+          <t>279381; 326198</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>359328; 405288</t>
+          <t>403042; 449349</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>394751; 459950</t>
+          <t>398387; 462779</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>430680; 497132</t>
+          <t>430222; 499089</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>513069; 578269</t>
+          <t>514431; 581335</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>678460; 754838</t>
+          <t>766621; 839995</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1702370</t>
+          <t>1841082</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2418607</t>
+          <t>2359947</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4120978</t>
+          <t>4201029</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1278406; 1386547</t>
+          <t>1269227; 1384329</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1662857; 1786307</t>
+          <t>1663717; 1778970</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1613679; 1736973</t>
+          <t>1622825; 1737555</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1311948; 1851087</t>
+          <t>1778830; 1904963</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1921725; 2034112</t>
+          <t>1919943; 2033055</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2433442; 2543822</t>
+          <t>2432896; 2545859</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2231949; 2348766</t>
+          <t>2229973; 2346123</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2308977; 2617178</t>
+          <t>2304519; 2413720</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3225281; 3389671</t>
+          <t>3227741; 3384674</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4129939; 4295748</t>
+          <t>4130369; 4307054</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3889010; 4051138</t>
+          <t>3884330; 4046399</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3651235; 4364087</t>
+          <t>4117241; 4284165</t>
         </is>
       </c>
     </row>
